--- a/00_Engine/InjectionTable_Engine/LoginSystem/LoginPython/AccountInfomation.xlsx
+++ b/00_Engine/InjectionTable_Engine/LoginSystem/LoginPython/AccountInfomation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="12960" windowHeight="4560"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerData" sheetId="1" r:id="rId1"/>
